--- a/勝一三合一單產生系統/地點代號對照表.xlsx
+++ b/勝一三合一單產生系統/地點代號對照表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,18 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>18P3A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EF180183A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/勝一三合一單產生系統/地點代號對照表.xlsx
+++ b/勝一三合一單產生系統/地點代號對照表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,26 @@
           <t>長代號</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>預設料號</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>IPA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>EBR</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>PGMEA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
